--- a/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
+++ b/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -143,6 +143,12 @@
   <si>
     <t>3002,3003</t>
   </si>
+  <si>
+    <t>四普通敌人</t>
+  </si>
+  <si>
+    <t>3001,3001,3001,3001</t>
+  </si>
 </sst>
 </file>
 
@@ -154,7 +160,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -208,6 +214,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -359,7 +370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -411,18 +422,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,156 +759,156 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -918,54 +917,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1437,14 +1443,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.7205882352941" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.9044117647059" style="2" customWidth="1"/>
     <col min="4" max="4" width="41.9044117647059" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="5" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
@@ -1549,6 +1555,17 @@
       </c>
       <c r="D8" s="19" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
+      <c r="B9" s="20">
+        <v>4005</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
+++ b/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
@@ -63,6 +63,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>敌人队伍</t>
     </r>
     <r>
@@ -80,6 +86,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>按顺序进入战斗的敌人</t>
     </r>
     <r>
@@ -147,7 +159,7 @@
     <t>四普通敌人</t>
   </si>
   <si>
-    <t>3001,3001,3001,3001</t>
+    <t>3001,3002,3001,3002</t>
   </si>
 </sst>
 </file>
@@ -908,7 +920,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -965,13 +977,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1443,7 +1452,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1523,48 +1532,70 @@
     </row>
     <row r="6" customHeight="1" spans="1:4">
       <c r="A6" s="16"/>
-      <c r="B6" s="17">
-        <v>4002</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>17</v>
-      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
     </row>
     <row r="7" customHeight="1" spans="1:4">
       <c r="A7" s="16"/>
       <c r="B7" s="17">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
       <c r="A8" s="16"/>
-      <c r="B8" s="17">
-        <v>4004</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>21</v>
-      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" customHeight="1" spans="1:4">
-      <c r="B9" s="20">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17">
+        <v>4003</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17">
+        <v>4004</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:4">
+      <c r="C12" s="20"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:4">
+      <c r="B13" s="2">
         <v>4005</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D13" s="21" t="s">
         <v>23</v>
       </c>
     </row>

--- a/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
+++ b/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>enemyIds</t>
   </si>
   <si>
+    <t>threatConfig</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -51,6 +54,9 @@
   </si>
   <si>
     <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t>EnemyPartyThreatLevel#ref=TbThreatLevelConfig</t>
   </si>
   <si>
     <t>##group</t>
@@ -82,7 +88,15 @@
     </r>
   </si>
   <si>
-    <t>显示名</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显示名</t>
+    </r>
   </si>
   <si>
     <r>
@@ -132,31 +146,90 @@
     </r>
   </si>
   <si>
-    <t>单敌人</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>威胁等级</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单敌人</t>
+    </r>
   </si>
   <si>
     <t>3001</t>
   </si>
   <si>
-    <t>双普通敌人</t>
+    <t>低</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>双普通敌人</t>
+    </r>
   </si>
   <si>
     <t>3001,3001</t>
   </si>
   <si>
-    <t>混合队伍</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>混合队伍</t>
+    </r>
   </si>
   <si>
     <t>3001,3002</t>
   </si>
   <si>
-    <t>高威胁队伍</t>
+    <t>中</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高威胁队伍</t>
+    </r>
   </si>
   <si>
     <t>3002,3003</t>
   </si>
   <si>
-    <t>四普通敌人</t>
+    <t>高</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四普通敌人</t>
+    </r>
   </si>
   <si>
     <t>3001,3002,3001,3002</t>
@@ -172,7 +245,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -209,15 +282,165 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -227,159 +450,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <name val="PingFang SC Regular"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -774,19 +852,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
@@ -795,132 +882,123 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -959,25 +1037,22 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
@@ -1452,17 +1527,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.7205882352941" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.9044117647059" style="2" customWidth="1"/>
     <col min="4" max="4" width="41.9044117647059" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.3014705882353" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1475,128 +1551,154 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:4">
+    <row r="2" customHeight="1" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:4">
+    <row r="3" customHeight="1" spans="1:5">
       <c r="A3" s="10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:4">
+    <row r="4" customHeight="1" spans="1:5">
       <c r="A4" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:4">
+    <row r="5" customHeight="1" spans="1:5">
       <c r="A5" s="16"/>
       <c r="B5" s="17">
         <v>4001</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>15</v>
+      <c r="C5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:4">
+    <row r="6" customHeight="1" spans="1:5">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
-    <row r="7" customHeight="1" spans="1:4">
+    <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="16"/>
       <c r="B7" s="17">
         <v>4002</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>17</v>
+      <c r="C7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:4">
+    <row r="8" customHeight="1" spans="1:5">
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="19"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
     </row>
-    <row r="9" customHeight="1" spans="1:4">
+    <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="16"/>
       <c r="B9" s="17">
         <v>4003</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>19</v>
+      <c r="C9" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:4">
+    <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
     </row>
-    <row r="11" customHeight="1" spans="1:4">
+    <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="16"/>
       <c r="B11" s="17">
         <v>4004</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>21</v>
+      <c r="C11" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:4">
-      <c r="C12" s="20"/>
+    <row r="12" customHeight="1" spans="1:5">
       <c r="D12" s="1"/>
     </row>
-    <row r="13" customHeight="1" spans="1:4">
+    <row r="13" customHeight="1" spans="1:5">
       <c r="B13" s="2">
         <v>4005</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>23</v>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
